--- a/media/tumski/text.xlsx
+++ b/media/tumski/text.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gala/Documents/Wroclaw/media/tumski/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B2BB18-9D2F-8B44-BE03-801AA89B1BFE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061E886B-B9ED-824D-95D6-9889C966D467}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="28040" windowHeight="16080" xr2:uid="{C59EF24E-31CD-9B41-8273-73354BB3CD1B}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15760" xr2:uid="{C59EF24E-31CD-9B41-8273-73354BB3CD1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Название достопримечательности</t>
   </si>
@@ -116,6 +116,15 @@
 Но самое интересное началось в 1893 году, когда на Тумский мост поселились святые. Первый — Иоанн Креститель, покровитель Вроцлавской Архиепархии, строгий, всевидящий. Вторая — святая Ядвига, берегиня Силезии, тихая, но не менее зоркая. Их изваял Густав Груненберг, и с тех пор они стоят, охраняя всех, кто ступает на этот мост.
 А ещё здесь появились фонари. Не простые, конечно, а газовые, зажигаемые вручную. Тогда, в XIX веке, это казалось чудом, но и теперь, в XXI, когда на мост опускается вечер, появляется фонарщик, зажигает свет, и в воздухе разливается тот самый старый Вроцлав.
 И, конечно, цвет. Тумский мост, не желая быть серым, выбрал зелёный. Так его и прозвали — Зелёным. Потому что в городе, где стены помнят, а мосты рассказывают истории, даже цвета имеют свои тайны.</t>
+  </si>
+  <si>
+    <t>На острове Тумский во Вроцлаве уже более тысячи лет стоят храмы, посвящённые святому Иоанну Крестителю. Первая деревянная святыня появилась, вероятно, ещё в X веке — следы её удалось обнаружить лишь при помощи георадара, и учёные до сих пор спорят о точной форме и датировке. В XI веке деревянный костёл сменил массивный романский — но он пал, по всей видимости, во время чешского нашествия. Новый романский костёл возвели к середине XII века, однако и он не простоял долго.
+С XIII по XIV век на его месте возникло настоящее готическое чудо — нынешний, уже четвёртый по счёту костёл. Именно он стал первой полностью готической постройкой на польских землях. Строительство шло постепенно: хор завершили около 1272 года, нефы и башни были готовы к 1341-му. Костёл не раз страдал от пожаров — например, в 1540 и 1759 годах — а в XIX–XX веках подвергался масштабной неоготической реставрации. Самое серьёзное разрушение он пережил после Второй мировой войны: около 70 % здания оказалось в руинах. Восстановление завершили к 1951 году, а купола башен вернулись лишь в 1991-м.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Костёл — это внушительное готическое здание, возведённое в XIII–XIV веках и ставшее первой полностью готической постройкой на польских землях. Это трёхнефная базилика с длинным хором и галереей (амбулаторией) вокруг алтаря, построенная из кирпича и камня. Его визитная карточка — две башни высотой почти 98 м, одна из которых ведёт на смотровую площадку с видом на Вроцлав и Одру. На фасаде — главный портал с богато украшенными скульптурами и резьбой, а боковые входы служат тонкими (но эффектными!) дополнениями к архитектурной симфонии сооружения .
+Внутри пространство ощущается высоким и воздушным: своды и витражи создают игру света и тени, словно вы очутились в сказочном зале. По периметру расположены готические и барочные капеллы, каждая с уникальным оформлением. Особенно впечатляют барочныe капеллы, построенные в XVII–XVIII веках, украшенные фресками и скульптурами, а также органы (в 1913 году), крупнейшие в Польше: внутри звучит музыка, которая кажется больше, чем музыка — это архетип звука ﻿.
+</t>
   </si>
 </sst>
 </file>
@@ -554,15 +563,19 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="238" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
       </c>

--- a/media/tumski/text.xlsx
+++ b/media/tumski/text.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gala/Documents/Wroclaw/media/tumski/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061E886B-B9ED-824D-95D6-9889C966D467}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044D1F8C-D0FE-DE43-ADFF-3B21B600E961}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15760" xr2:uid="{C59EF24E-31CD-9B41-8273-73354BB3CD1B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Название достопримечательности</t>
   </si>
@@ -39,27 +39,12 @@
     <t>Кафедральный собор Святого Иоанна Крестителя</t>
   </si>
   <si>
-    <t>Главный католический храм Вроцлава, построенный в готическом стиле. Его 98-метровые башни видны издалека.</t>
-  </si>
-  <si>
-    <t>Собор считается первым полностью готическим храмом в Польше. Во время Второй мировой войны был сильно поврежден и восстановлен в послевоенные годы.</t>
-  </si>
-  <si>
     <t>Тумский мост</t>
   </si>
   <si>
-    <t>Считается, что если пара повесит замок на мосту и выбросит ключ в реку, их любовь будет вечной.</t>
-  </si>
-  <si>
     <t>Костёл Святого Креста и Святого Варфоломея</t>
   </si>
   <si>
-    <t>Двухэтажный готический храм, уникальный для Польши. Нижний уровень посвящен Святому Варфоломею, верхний — Святому Кресту.</t>
-  </si>
-  <si>
-    <t>Согласно легенде, храм был построен князем Генрихом IV Пробусом в благодарность за спасение во время охоты.</t>
-  </si>
-  <si>
     <t>Дворец архиепископа</t>
   </si>
   <si>
@@ -94,9 +79,6 @@
   </si>
   <si>
     <t>Архитектура</t>
-  </si>
-  <si>
-    <t>Если Вроцлав — это город-сказка (а он, безусловно, именно таков), то Тумский мост — это тот самый волшебный портал, который ведёт в его самое древнее и таинственное сердце. Название у него, конечно, звучное и важное — «кафедральный», потому что ведёт он прямиком к величественному Собору Святого Иоанна Крестителя. А ещё потому, что старина Тумский — не просто мост, а граница между мирами: когда-то тут сходились светская власть и церковная, и даже специальный столб с двумя гербами поставили, чтобы никто не забыл, кто тут главный (впрочем, это не помогало).</t>
   </si>
   <si>
     <t>Остров Тумский — это не просто место на карте, а настоящий временной портал, ведущий прямиком в глубины веков. Если Вроцлав был бы старинной книгой, то его первая глава начиналась бы именно здесь, в X веке, среди туманов, колокольного звона и таинственных силуэтов.
@@ -104,27 +86,69 @@
 Так что приготовьтесь. Мы начнем нашу прогулку с Тумского моста и шаг за шагом будем разгадывать тайны средневекового Вроцлава. А если вдруг услышите шёпот старых стен — не пугайтесь. Это просто остров рассказывает вам свои истории.</t>
   </si>
   <si>
+    <t>В городе иногда бывают места, которые почему-то кажутся тебе живыми. Не потому, что по ним постоянно ходят люди или пробегают коты. Живыми в другом смысле.</t>
+  </si>
+  <si>
+    <t>Когда-то здесь был обычный деревянный мост. Настолько старый, что помнил рождение города. Он соединял два совершенно разных мира: один мир был у церкви, другой — у мирян. И, как это обычно бывает, мост стал единственным местом, где миры могли пересекаться без претензий и лишних вопросов.</t>
+  </si>
+  <si>
+    <t>Потом пришёл XIX век и сказал: «Хватит романтики, давайте уже что-нибудь серьёзное». Так в 1889 году появился стальной красавец с заклёпками, построенный под чутким взглядом инженера фон Шольца. Мост пережил войны, ремонты и даже период, когда на него вечно кто-то вешал замки с сердечками. Всё это он перенёс с тем же философским спокойствием, с каким старые кошки переносят очередную перестановку мебели.</t>
+  </si>
+  <si>
+    <t>На первый взгляд — просто железный мост длиной 52 метра. Два пролёта, тротуары, проезжая часть, и всё это под аккуратной неоготической «шляпой», которая, честно говоря, нужна только для красоты. На второй взгляд — он напоминает музыкальный инструмент: каждый пролёт, как струна, и если сильно прислушаться (а ещё лучше, прийти ночью), можно услышать его задумчивые мелодии.</t>
+  </si>
+  <si>
+    <t>Ферма Гербера, сталь, заклёпки, аккуратные пропорции — всё это инженерная поэзия. А чтобы его собрать, детали привозили по воде на баржах. Словно это не просто проект, а какой-то магический ритуал, где каждый болт должен приплыть по реке. &lt;br&gt; Чтобы мосту было спокойнее жить на своём месте.</t>
+  </si>
+  <si>
     <t xml:space="preserve">
-Мосты, как известно, живые существа, и этот не исключение. Он то рушился, то возрождался, как настоящий герой древнего эпоса. В 1423 году он не выдержал людского усердия: в Вербное воскресенье толпа верующих заполнила его до отказа, и — ах! — дерево не выдержало, судьба распорядилась иначе. С тех пор каждый, кто ступает сюда, будто слышит отголоски того дня.
-Долгое время мост был деревянным и скромным, таким, каким бывают мосты, пока архитекторы не решат, что пора бы их улучшить. XIX век принёс технологии и амбиции, и вот уже Тумский мост меняет свой облик, становится прочнее, наряднее. Но история жестока к красивым вещам: в 1945 году война обрушила на него всю свою ярость, и он, как и весь город, сильно пострадал.
-Но, как водится, чудеса случаются: Тумский мост восстановили, и теперь он стоит, как прежде, соединяя эпохи, легенды и любопытных путешественников. В 1976 году он даже попал в реестр памятников Польши — видимо, чтобы его больше не забывали и берегли. Хотя настоящая магия Тумского моста вовсе не в бумажках и официальных записях. Просто перейдите его на закате, когда зажигаются старые фонари, и почувствуете: он жив, он помнит.</t>
-  </si>
-  <si>
-    <t>Тумский мост, как и всякий уважающий себя мост, знал времена и похуже. Когда-то он был скромным деревянным настилом, покорно терпел шаги путников, лязг колес и даже ненароком сброшенные в воду монеты. Но в 1889 году его судьба изменилась: явился архитектор Альфред фон Шольц, задумчиво оглядел ветхий настил и решил — пора бы заменить. Так и появился новый мост, из стали и заклёпок, блестящий, крепкий, словно специально выкованный для путешествий между мирами.
-Говорят, что его образец где-то в далёком Мангейме даже получил награду, но Тумский оказался лучше — с двумя пролетами и гордой осанкой. Не сказать, что он был велик — всего-то 52 метра в длину, 7 метров в ширину, — но разве в размерах дело?
-Строили его неспешно, обстоятельно. Металл отливали на заводе в Рудзинце, аж в 150 километрах от Вроцлава. А чтобы переправить эту тяжесть, пришлось пустить её по воде, на барже, ведь иной способ был бы слишком дорог — даже мостам приходится экономить.
-Но самое интересное началось в 1893 году, когда на Тумский мост поселились святые. Первый — Иоанн Креститель, покровитель Вроцлавской Архиепархии, строгий, всевидящий. Вторая — святая Ядвига, берегиня Силезии, тихая, но не менее зоркая. Их изваял Густав Груненберг, и с тех пор они стоят, охраняя всех, кто ступает на этот мост.
-А ещё здесь появились фонари. Не простые, конечно, а газовые, зажигаемые вручную. Тогда, в XIX веке, это казалось чудом, но и теперь, в XXI, когда на мост опускается вечер, появляется фонарщик, зажигает свет, и в воздухе разливается тот самый старый Вроцлав.
-И, конечно, цвет. Тумский мост, не желая быть серым, выбрал зелёный. Так его и прозвали — Зелёным. Потому что в городе, где стены помнят, а мосты рассказывают истории, даже цвета имеют свои тайны.</t>
-  </si>
-  <si>
-    <t>На острове Тумский во Вроцлаве уже более тысячи лет стоят храмы, посвящённые святому Иоанну Крестителю. Первая деревянная святыня появилась, вероятно, ещё в X веке — следы её удалось обнаружить лишь при помощи георадара, и учёные до сих пор спорят о точной форме и датировке. В XI веке деревянный костёл сменил массивный романский — но он пал, по всей видимости, во время чешского нашествия. Новый романский костёл возвели к середине XII века, однако и он не простоял долго.
-С XIII по XIV век на его месте возникло настоящее готическое чудо — нынешний, уже четвёртый по счёту костёл. Именно он стал первой полностью готической постройкой на польских землях. Строительство шло постепенно: хор завершили около 1272 года, нефы и башни были готовы к 1341-му. Костёл не раз страдал от пожаров — например, в 1540 и 1759 годах — а в XIX–XX веках подвергался масштабной неоготической реставрации. Самое серьёзное разрушение он пережил после Второй мировой войны: около 70 % здания оказалось в руинах. Восстановление завершили к 1951 году, а купола башен вернулись лишь в 1991-м.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Костёл — это внушительное готическое здание, возведённое в XIII–XIV веках и ставшее первой полностью готической постройкой на польских землях. Это трёхнефная базилика с длинным хором и галереей (амбулаторией) вокруг алтаря, построенная из кирпича и камня. Его визитная карточка — две башни высотой почти 98 м, одна из которых ведёт на смотровую площадку с видом на Вроцлав и Одру. На фасаде — главный портал с богато украшенными скульптурами и резьбой, а боковые входы служат тонкими (но эффектными!) дополнениями к архитектурной симфонии сооружения .
-Внутри пространство ощущается высоким и воздушным: своды и витражи создают игру света и тени, словно вы очутились в сказочном зале. По периметру расположены готические и барочные капеллы, каждая с уникальным оформлением. Особенно впечатляют барочныe капеллы, построенные в XVII–XVIII веках, украшенные фресками и скульптурами, а также органы (в 1913 году), крупнейшие в Польше: внутри звучит музыка, которая кажется больше, чем музыка — это архетип звука ﻿.
-</t>
+В начале XXI века он стал мостом влюблённых. Люди вешали замочки, бросали ключи в Одру и уходили, уверенные, что теперь их любовь будет вечной. Мост, конечно, молчал и ничего не обещал. Потом власти решили, что для железного сердца это слишком тяжело, и сняли всё это добро. С тех пор новые замки исчезают так же быстро, как иллюзии после утреннего кофе.</t>
+  </si>
+  <si>
+    <t>А ещё у моста есть друг-фонарщик. Настоящий, живой. Каждый вечер он зажигает газовые фонари на Тумском острове. Кажется, он знает что-то, чего мы с вами никогда не узнаем. Может быть, он даже хранит общие тайны с мостом. 
+И если однажды вы задержитесь на этом месте чуть дольше, чем планировали, мост вполне может вам их поведать. Только тихо. &lt;br&gt; Чтобы никто больше не узнал.</t>
+  </si>
+  <si>
+    <t>На Тумском острове собор Святого Иоанна Крестителя стоит так давно, что кажется, он сам уже забыл, сколько раз рождался заново. Первая деревянная церковь здесь появилась ещё в X веке — и теперь о ней напоминают только призрачные следы в земле, которые можно разглядеть лишь с помощью хитрого георадара. Потом её сменяли романские храмы: один рухнул во время чешского нашествия, другой не выдержал времени. И только в XIII–XIV веках на этом месте вырос нынешний каменный великан — первая по-настоящему готическая постройка на польских землях.</t>
+  </si>
+  <si>
+    <t>С тех пор он много раз горел, рушился и поднимался снова. Пожары в XVI и XVIII веках, неоготическая реставрация в XIX, ужасы Второй мировой, когда почти три четверти собора превратились в груду камней… Но он снова встал. К 1951-му его восстановили, а башни с медными куполами вернулись только в 1991-м, словно в последний раз напомнив: этот собор может пережить всё. И продолжает стоять — каменное сердце города, которое бьётся уже тысячу лет.</t>
+  </si>
+  <si>
+    <t>Собор в готике — это не просто здание, а настоящий каменный фокус: трёхнефная базилика, вытянутая, будто стремится дотянуться до неба, с галереей, чтобы можно было обойти алтарь, словно обойти центр мира. Две башни почти по сто метров высотой подмигивают городу: одна просто стоит, другая приглашает подняться и посмотреть на Вроцлав сверху, как на игрушечный макет, где Одра — серебряная лента, а крыши — красные черепичные квадратики. Фасад встречает порталами и скульптурами так щедро, что кажется, сама стена решила рассказать сказку.</t>
+  </si>
+  <si>
+    <t>А внутри всё ещё удивительнее: воздух там не висит, а парит под сводами, и витражи раскладывают свет на кусочки, будто кто-то рассыпал по залу разноцветное стекло. В капеллах притаились готические и барочные истории: где-то строгие каменные линии, а где-то барокко, расплескавшееся фресками и ангелами. А орган — отдельная глава: установленный в 1913-м, он до сих пор звучит так, словно весь собор становится огромным музыкальным инструментом. И в какой-то момент ты понимаешь, что это не музыка, а сама память города, которая вдруг заговорила звуком.</t>
+  </si>
+  <si>
+    <t>Когда над Вроцлавом развевался шторм артиллерийских залпов, один снаряд умудрился попасть в стену Собора Святого Иоанна Крестителя и застрять там — не до конца, но и не настолько, чтобы его вытащили. И вот он, этот кусочек войны, всё ещё там. Как каменное напоминание о том, что время может заживлять раны. &lt;br&gt; Но не стирает шрамов.</t>
+  </si>
+  <si>
+    <t>Это не храм, а огромная книга, написанная на камне и кирпиче. Его башни тянутся в небо, будто сами хотят рассказать, что Вроцлав уже видел всё: и войны, и пожары, и воду по колено, и всё равно каждый раз поднимался, отряхивался и шёл дальше. Внутри собора — не просто витражи и алтари, а целый музей, спрятанный за молитвой. А орган… орган звучит так, будто сам воздух вдруг вспоминает, что он умеет петь, и поёт лучше всех в Европе.</t>
+  </si>
+  <si>
+    <t>Многие проходят мимо, глядя на устремлённые в небо башни, портал и капеллы. Но устремите взгляд на одну из стен — там у башенок, будто затаившись в тени, где-то между архангелами и резьбой, сидит человеческое лицо с открытым ртом, словно оно только что увидело нечто ужасное и не может промолчать. Это не просто камень — это каменная гримаса, оставленная мастером, который мог позволить себе шёпот и улыбку даже в эпоху готики.</t>
+  </si>
+  <si>
+    <t>Эта церковь родилась из упрямого желания примирить князя Генрика IV Пробуса и епископа Томаша II. В конце XIII века оба, устав от взаимных обид, решили построить храм — чтобы и Богу угодить, и самим помириться. Так в 1288–1295 годах начался фундамент, а к середине XIV века, под присмотром мастера Виланда, стены уже тянулись в небо.</t>
+  </si>
+  <si>
+    <t>Со временем храм успел пережить всё, что только возможно: его нижний этаж превращался то в склад, то в конюшню, то в убежище. Верхний же, будто гордый старший брат, продолжал хранить молитвы и органные аккорды. Войны, пожары, реставрации — всё это оставило следы, но не разрушило его окончательно. Даже после Второй мировой, когда многие святыни лежали в руинах, он снова поднялся — и теперь стоит, как каменный свидетель того, что жизнь всё равно сильнее разрушений.</t>
+  </si>
+  <si>
+    <t>На Тумском острове есть храм, который на первый взгляд напоминает хитроумную шкатулку с двойным дном. Снаружи — обычное готическое чудо с башенками и арками, а внутри вдруг оказывается два уровня: верхний для света, нижний для тени. И каждый этаж словно живёт своей жизнью — как будто вы попали в дом, где два поколения не разговаривают друг с другом, но всё равно мирно делят крышу.</t>
+  </si>
+  <si>
+    <t>Самое удивительное в этой церкви — её двойная натура. Нижний уровень, посвящённый Святому Варфоломею, выглядит сурово и основательно, словно крепость, готовая выдержать любой натиск. Здесь низкие своды и тёмные углы, где хочется шептаться, а не разговаривать вслух.</t>
+  </si>
+  <si>
+    <t>А верхний уровень, посвящённый Святому Кресту, напротив, весь соткан из воздуха и света. Огромные окна впускают солнце, своды стремятся к небу, и создаётся впечатление, что храм сам по себе поёт. Здесь когда-то сидели каноники, здесь же и сейчас музыка органа разливается так, будто стены умеют дышать.</t>
+  </si>
+  <si>
+    <t>Есть в этой церкви и маленькая загадка, достойная хорошей городской легенды. Князь Генрик IV хотел, чтобы его похоронили именно здесь, в нижнем храме, «пока не построят мавзолей». Но судьба оказалась насмешливой: мавзолей так и не появился, а во время Второй мировой его останки куда-то исчезли. Одни говорят — увезли немцы, другие шепчут — сам ушёл, чтобы больше не смотреть на войны.</t>
+  </si>
+  <si>
+    <t>И ещё: в отличие от многих храмов, где пространство строго вертикально — от земли к небу, здесь всё устроено горизонтально-вертикально одновременно. Два этажа, два характера, два пути. Словно храм не выбирает между светом и тьмой, а даёт каждому своё место. И, возможно, именно поэтому он кажется живым — потому что признаёт в человеке и земное, и небесное сразу.</t>
   </si>
 </sst>
 </file>
@@ -503,17 +527,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCC9D9F-23E5-F94F-84B8-3F770A35914B}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="2" max="2" width="57.1640625" customWidth="1"/>
-    <col min="3" max="3" width="120.83203125" customWidth="1"/>
-    <col min="4" max="4" width="85.6640625" customWidth="1"/>
-    <col min="5" max="5" width="51.1640625" customWidth="1"/>
+    <col min="2" max="2" width="40.1640625" customWidth="1"/>
+    <col min="3" max="3" width="41.1640625" customWidth="1"/>
+    <col min="4" max="4" width="55.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" customWidth="1"/>
+    <col min="6" max="6" width="85.6640625" customWidth="1"/>
+    <col min="7" max="7" width="51.1640625" customWidth="1"/>
+    <col min="8" max="8" width="48.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -521,131 +548,170 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D1" s="3"/>
       <c r="E1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" ht="323" x14ac:dyDescent="0.2">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="2"/>
+        <v>18</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="408" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="145" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="238" x14ac:dyDescent="0.2">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="243" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="170" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="G7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/media/tumski/text.xlsx
+++ b/media/tumski/text.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gala/Documents/Wroclaw/media/tumski/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044D1F8C-D0FE-DE43-ADFF-3B21B600E961}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFC5C19-92F3-F84E-B20A-2CFA3517C602}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15760" xr2:uid="{C59EF24E-31CD-9B41-8273-73354BB3CD1B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Название достопримечательности</t>
   </si>
@@ -81,74 +81,116 @@
     <t>Архитектура</t>
   </si>
   <si>
-    <t>Остров Тумский — это не просто место на карте, а настоящий временной портал, ведущий прямиком в глубины веков. Если Вроцлав был бы старинной книгой, то его первая глава начиналась бы именно здесь, в X веке, среди туманов, колокольного звона и таинственных силуэтов.
+    <t>В городе иногда бывают места, которые почему-то кажутся тебе живыми. Не потому, что по ним постоянно ходят люди или пробегают коты. Живыми в другом смысле.</t>
+  </si>
+  <si>
+    <t>Когда-то здесь был обычный деревянный мост. Настолько старый, что помнил рождение города. Он соединял два совершенно разных мира: один мир был у церкви, другой — у мирян. И, как это обычно бывает, мост стал единственным местом, где миры могли пересекаться без претензий и лишних вопросов.</t>
+  </si>
+  <si>
+    <t>Потом пришёл XIX век и сказал: «Хватит романтики, давайте уже что-нибудь серьёзное». Так в 1889 году появился стальной красавец с заклёпками, построенный под чутким взглядом инженера фон Шольца. Мост пережил войны, ремонты и даже период, когда на него вечно кто-то вешал замки с сердечками. Всё это он перенёс с тем же философским спокойствием, с каким старые кошки переносят очередную перестановку мебели.</t>
+  </si>
+  <si>
+    <t>На первый взгляд — просто железный мост длиной 52 метра. Два пролёта, тротуары, проезжая часть, и всё это под аккуратной неоготической «шляпой», которая, честно говоря, нужна только для красоты. На второй взгляд — он напоминает музыкальный инструмент: каждый пролёт, как струна, и если сильно прислушаться (а ещё лучше, прийти ночью), можно услышать его задумчивые мелодии.</t>
+  </si>
+  <si>
+    <t>Ферма Гербера, сталь, заклёпки, аккуратные пропорции — всё это инженерная поэзия. А чтобы его собрать, детали привозили по воде на баржах. Словно это не просто проект, а какой-то магический ритуал, где каждый болт должен приплыть по реке. &lt;br&gt; Чтобы мосту было спокойнее жить на своём месте.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+В начале XXI века он стал мостом влюблённых. Люди вешали замочки, бросали ключи в Одру и уходили, уверенные, что теперь их любовь будет вечной. Мост, конечно, молчал и ничего не обещал. Потом власти решили, что для железного сердца это слишком тяжело, и сняли всё это добро. С тех пор новые замки исчезают так же быстро, как иллюзии после утреннего кофе.</t>
+  </si>
+  <si>
+    <t>А ещё у моста есть друг-фонарщик. Настоящий, живой. Каждый вечер он зажигает газовые фонари на Тумском острове. Кажется, он знает что-то, чего мы с вами никогда не узнаем. Может быть, он даже хранит общие тайны с мостом. 
+И если однажды вы задержитесь на этом месте чуть дольше, чем планировали, мост вполне может вам их поведать. Только тихо. &lt;br&gt; Чтобы никто больше не узнал.</t>
+  </si>
+  <si>
+    <t>На Тумском острове собор Святого Иоанна Крестителя стоит так давно, что кажется, он сам уже забыл, сколько раз рождался заново. Первая деревянная церковь здесь появилась ещё в X веке — и теперь о ней напоминают только призрачные следы в земле, которые можно разглядеть лишь с помощью хитрого георадара. Потом её сменяли романские храмы: один рухнул во время чешского нашествия, другой не выдержал времени. И только в XIII–XIV веках на этом месте вырос нынешний каменный великан — первая по-настоящему готическая постройка на польских землях.</t>
+  </si>
+  <si>
+    <t>С тех пор он много раз горел, рушился и поднимался снова. Пожары в XVI и XVIII веках, неоготическая реставрация в XIX, ужасы Второй мировой, когда почти три четверти собора превратились в груду камней… Но он снова встал. К 1951-му его восстановили, а башни с медными куполами вернулись только в 1991-м, словно в последний раз напомнив: этот собор может пережить всё. И продолжает стоять — каменное сердце города, которое бьётся уже тысячу лет.</t>
+  </si>
+  <si>
+    <t>Собор в готике — это не просто здание, а настоящий каменный фокус: трёхнефная базилика, вытянутая, будто стремится дотянуться до неба, с галереей, чтобы можно было обойти алтарь, словно обойти центр мира. Две башни почти по сто метров высотой подмигивают городу: одна просто стоит, другая приглашает подняться и посмотреть на Вроцлав сверху, как на игрушечный макет, где Одра — серебряная лента, а крыши — красные черепичные квадратики. Фасад встречает порталами и скульптурами так щедро, что кажется, сама стена решила рассказать сказку.</t>
+  </si>
+  <si>
+    <t>А внутри всё ещё удивительнее: воздух там не висит, а парит под сводами, и витражи раскладывают свет на кусочки, будто кто-то рассыпал по залу разноцветное стекло. В капеллах притаились готические и барочные истории: где-то строгие каменные линии, а где-то барокко, расплескавшееся фресками и ангелами. А орган — отдельная глава: установленный в 1913-м, он до сих пор звучит так, словно весь собор становится огромным музыкальным инструментом. И в какой-то момент ты понимаешь, что это не музыка, а сама память города, которая вдруг заговорила звуком.</t>
+  </si>
+  <si>
+    <t>Когда над Вроцлавом развевался шторм артиллерийских залпов, один снаряд умудрился попасть в стену Собора Святого Иоанна Крестителя и застрять там — не до конца, но и не настолько, чтобы его вытащили. И вот он, этот кусочек войны, всё ещё там. Как каменное напоминание о том, что время может заживлять раны. &lt;br&gt; Но не стирает шрамов.</t>
+  </si>
+  <si>
+    <t>Это не храм, а огромная книга, написанная на камне и кирпиче. Его башни тянутся в небо, будто сами хотят рассказать, что Вроцлав уже видел всё: и войны, и пожары, и воду по колено, и всё равно каждый раз поднимался, отряхивался и шёл дальше. Внутри собора — не просто витражи и алтари, а целый музей, спрятанный за молитвой. А орган… орган звучит так, будто сам воздух вдруг вспоминает, что он умеет петь, и поёт лучше всех в Европе.</t>
+  </si>
+  <si>
+    <t>Многие проходят мимо, глядя на устремлённые в небо башни, портал и капеллы. Но устремите взгляд на одну из стен — там у башенок, будто затаившись в тени, где-то между архангелами и резьбой, сидит человеческое лицо с открытым ртом, словно оно только что увидело нечто ужасное и не может промолчать. Это не просто камень — это каменная гримаса, оставленная мастером, который мог позволить себе шёпот и улыбку даже в эпоху готики.</t>
+  </si>
+  <si>
+    <t>Эта церковь родилась из упрямого желания примирить князя Генрика IV Пробуса и епископа Томаша II. В конце XIII века оба, устав от взаимных обид, решили построить храм — чтобы и Богу угодить, и самим помириться. Так в 1288–1295 годах начался фундамент, а к середине XIV века, под присмотром мастера Виланда, стены уже тянулись в небо.</t>
+  </si>
+  <si>
+    <t>Со временем храм успел пережить всё, что только возможно: его нижний этаж превращался то в склад, то в конюшню, то в убежище. Верхний же, будто гордый старший брат, продолжал хранить молитвы и органные аккорды. Войны, пожары, реставрации — всё это оставило следы, но не разрушило его окончательно. Даже после Второй мировой, когда многие святыни лежали в руинах, он снова поднялся — и теперь стоит, как каменный свидетель того, что жизнь всё равно сильнее разрушений.</t>
+  </si>
+  <si>
+    <t>На Тумском острове есть храм, который на первый взгляд напоминает хитроумную шкатулку с двойным дном. Снаружи — обычное готическое чудо с башенками и арками, а внутри вдруг оказывается два уровня: верхний для света, нижний для тени. И каждый этаж словно живёт своей жизнью — как будто вы попали в дом, где два поколения не разговаривают друг с другом, но всё равно мирно делят крышу.</t>
+  </si>
+  <si>
+    <t>Самое удивительное в этой церкви — её двойная натура. Нижний уровень, посвящённый Святому Варфоломею, выглядит сурово и основательно, словно крепость, готовая выдержать любой натиск. Здесь низкие своды и тёмные углы, где хочется шептаться, а не разговаривать вслух.</t>
+  </si>
+  <si>
+    <t>А верхний уровень, посвящённый Святому Кресту, напротив, весь соткан из воздуха и света. Огромные окна впускают солнце, своды стремятся к небу, и создаётся впечатление, что храм сам по себе поёт. Здесь когда-то сидели каноники, здесь же и сейчас музыка органа разливается так, будто стены умеют дышать.</t>
+  </si>
+  <si>
+    <t>Есть в этой церкви и маленькая загадка, достойная хорошей городской легенды. Князь Генрик IV хотел, чтобы его похоронили именно здесь, в нижнем храме, «пока не построят мавзолей». Но судьба оказалась насмешливой: мавзолей так и не появился, а во время Второй мировой его останки куда-то исчезли. Одни говорят — увезли немцы, другие шепчут — сам ушёл, чтобы больше не смотреть на войны.</t>
+  </si>
+  <si>
+    <t>И ещё: в отличие от многих храмов, где пространство строго вертикально — от земли к небу, здесь всё устроено горизонтально-вертикально одновременно. Два этажа, два характера, два пути. Словно храм не выбирает между светом и тьмой, а даёт каждому своё место. И, возможно, именно поэтому он кажется живым — потому что признаёт в человеке и земное, и небесное сразу.</t>
+  </si>
+  <si>
+    <t>Остров Тумский — это не просто место на карте, а настоящий временной портал, ведущий прямиком в глубины веков. Если Вроцлав был бы старинной книгой, то его первая глава начиналась бы именно здесь, в X веке, среди туманов, колокольного звона и таинственных сОстров Тумский — это не просто место на карте, а настоящий временной портал, ведущий прямиком в глубины веков. Если бы Вроцлав был старинной книгой, то его первая глава начиналась бы именно здесь, в X веке, среди туманов, колокольного звона и таинственных силуэтов. &lt;br&gt;Этот остров — не просто район, а целая энциклопедия чудес. Здесь древние храмы соседствуют с причудливыми легендами, улицы шепчутся о прошлом, а по вечерам, словно по волшебству, появляется фонарщик. Да-да, самый настоящий, в длинном плаще, с фонарем и специальной палочкой. И каждую ночь он вручную зажигает старые газовые фонари, как будто напоминая городу, что магия ещё жива.&lt;br&gt;Так что приготовьтесь. Мы начнем нашу прогулку с Тумского моста и шаг за шагом будем разгадывать тайны средневекового Вроцлава. А если вдруг услышите шёпот старых стен — не пугайтесь. Это просто остров рассказывает вам свои истории.илуэтов.
 Этот остров — не просто район, а целая энциклопедия чудес. Здесь древние храмы соседствуют с причудливыми легендами, улицы шепчутся о прошлом, а по вечерам, словно по волшебству, появляется фонарщик. Да-да, самый настоящий, в длинном плаще, с фонарем и специальной палочкой. И каждую ночь он вручную зажигает старые газовые фонари, как будто напоминая городу, что магия ещё жива.
 Так что приготовьтесь. Мы начнем нашу прогулку с Тумского моста и шаг за шагом будем разгадывать тайны средневекового Вроцлава. А если вдруг услышите шёпот старых стен — не пугайтесь. Это просто остров рассказывает вам свои истории.</t>
   </si>
   <si>
-    <t>В городе иногда бывают места, которые почему-то кажутся тебе живыми. Не потому, что по ним постоянно ходят люди или пробегают коты. Живыми в другом смысле.</t>
-  </si>
-  <si>
-    <t>Когда-то здесь был обычный деревянный мост. Настолько старый, что помнил рождение города. Он соединял два совершенно разных мира: один мир был у церкви, другой — у мирян. И, как это обычно бывает, мост стал единственным местом, где миры могли пересекаться без претензий и лишних вопросов.</t>
-  </si>
-  <si>
-    <t>Потом пришёл XIX век и сказал: «Хватит романтики, давайте уже что-нибудь серьёзное». Так в 1889 году появился стальной красавец с заклёпками, построенный под чутким взглядом инженера фон Шольца. Мост пережил войны, ремонты и даже период, когда на него вечно кто-то вешал замки с сердечками. Всё это он перенёс с тем же философским спокойствием, с каким старые кошки переносят очередную перестановку мебели.</t>
-  </si>
-  <si>
-    <t>На первый взгляд — просто железный мост длиной 52 метра. Два пролёта, тротуары, проезжая часть, и всё это под аккуратной неоготической «шляпой», которая, честно говоря, нужна только для красоты. На второй взгляд — он напоминает музыкальный инструмент: каждый пролёт, как струна, и если сильно прислушаться (а ещё лучше, прийти ночью), можно услышать его задумчивые мелодии.</t>
-  </si>
-  <si>
-    <t>Ферма Гербера, сталь, заклёпки, аккуратные пропорции — всё это инженерная поэзия. А чтобы его собрать, детали привозили по воде на баржах. Словно это не просто проект, а какой-то магический ритуал, где каждый болт должен приплыть по реке. &lt;br&gt; Чтобы мосту было спокойнее жить на своём месте.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-В начале XXI века он стал мостом влюблённых. Люди вешали замочки, бросали ключи в Одру и уходили, уверенные, что теперь их любовь будет вечной. Мост, конечно, молчал и ничего не обещал. Потом власти решили, что для железного сердца это слишком тяжело, и сняли всё это добро. С тех пор новые замки исчезают так же быстро, как иллюзии после утреннего кофе.</t>
-  </si>
-  <si>
-    <t>А ещё у моста есть друг-фонарщик. Настоящий, живой. Каждый вечер он зажигает газовые фонари на Тумском острове. Кажется, он знает что-то, чего мы с вами никогда не узнаем. Может быть, он даже хранит общие тайны с мостом. 
-И если однажды вы задержитесь на этом месте чуть дольше, чем планировали, мост вполне может вам их поведать. Только тихо. &lt;br&gt; Чтобы никто больше не узнал.</t>
-  </si>
-  <si>
-    <t>На Тумском острове собор Святого Иоанна Крестителя стоит так давно, что кажется, он сам уже забыл, сколько раз рождался заново. Первая деревянная церковь здесь появилась ещё в X веке — и теперь о ней напоминают только призрачные следы в земле, которые можно разглядеть лишь с помощью хитрого георадара. Потом её сменяли романские храмы: один рухнул во время чешского нашествия, другой не выдержал времени. И только в XIII–XIV веках на этом месте вырос нынешний каменный великан — первая по-настоящему готическая постройка на польских землях.</t>
-  </si>
-  <si>
-    <t>С тех пор он много раз горел, рушился и поднимался снова. Пожары в XVI и XVIII веках, неоготическая реставрация в XIX, ужасы Второй мировой, когда почти три четверти собора превратились в груду камней… Но он снова встал. К 1951-му его восстановили, а башни с медными куполами вернулись только в 1991-м, словно в последний раз напомнив: этот собор может пережить всё. И продолжает стоять — каменное сердце города, которое бьётся уже тысячу лет.</t>
-  </si>
-  <si>
-    <t>Собор в готике — это не просто здание, а настоящий каменный фокус: трёхнефная базилика, вытянутая, будто стремится дотянуться до неба, с галереей, чтобы можно было обойти алтарь, словно обойти центр мира. Две башни почти по сто метров высотой подмигивают городу: одна просто стоит, другая приглашает подняться и посмотреть на Вроцлав сверху, как на игрушечный макет, где Одра — серебряная лента, а крыши — красные черепичные квадратики. Фасад встречает порталами и скульптурами так щедро, что кажется, сама стена решила рассказать сказку.</t>
-  </si>
-  <si>
-    <t>А внутри всё ещё удивительнее: воздух там не висит, а парит под сводами, и витражи раскладывают свет на кусочки, будто кто-то рассыпал по залу разноцветное стекло. В капеллах притаились готические и барочные истории: где-то строгие каменные линии, а где-то барокко, расплескавшееся фресками и ангелами. А орган — отдельная глава: установленный в 1913-м, он до сих пор звучит так, словно весь собор становится огромным музыкальным инструментом. И в какой-то момент ты понимаешь, что это не музыка, а сама память города, которая вдруг заговорила звуком.</t>
-  </si>
-  <si>
-    <t>Когда над Вроцлавом развевался шторм артиллерийских залпов, один снаряд умудрился попасть в стену Собора Святого Иоанна Крестителя и застрять там — не до конца, но и не настолько, чтобы его вытащили. И вот он, этот кусочек войны, всё ещё там. Как каменное напоминание о том, что время может заживлять раны. &lt;br&gt; Но не стирает шрамов.</t>
-  </si>
-  <si>
-    <t>Это не храм, а огромная книга, написанная на камне и кирпиче. Его башни тянутся в небо, будто сами хотят рассказать, что Вроцлав уже видел всё: и войны, и пожары, и воду по колено, и всё равно каждый раз поднимался, отряхивался и шёл дальше. Внутри собора — не просто витражи и алтари, а целый музей, спрятанный за молитвой. А орган… орган звучит так, будто сам воздух вдруг вспоминает, что он умеет петь, и поёт лучше всех в Европе.</t>
-  </si>
-  <si>
-    <t>Многие проходят мимо, глядя на устремлённые в небо башни, портал и капеллы. Но устремите взгляд на одну из стен — там у башенок, будто затаившись в тени, где-то между архангелами и резьбой, сидит человеческое лицо с открытым ртом, словно оно только что увидело нечто ужасное и не может промолчать. Это не просто камень — это каменная гримаса, оставленная мастером, который мог позволить себе шёпот и улыбку даже в эпоху готики.</t>
-  </si>
-  <si>
-    <t>Эта церковь родилась из упрямого желания примирить князя Генрика IV Пробуса и епископа Томаша II. В конце XIII века оба, устав от взаимных обид, решили построить храм — чтобы и Богу угодить, и самим помириться. Так в 1288–1295 годах начался фундамент, а к середине XIV века, под присмотром мастера Виланда, стены уже тянулись в небо.</t>
-  </si>
-  <si>
-    <t>Со временем храм успел пережить всё, что только возможно: его нижний этаж превращался то в склад, то в конюшню, то в убежище. Верхний же, будто гордый старший брат, продолжал хранить молитвы и органные аккорды. Войны, пожары, реставрации — всё это оставило следы, но не разрушило его окончательно. Даже после Второй мировой, когда многие святыни лежали в руинах, он снова поднялся — и теперь стоит, как каменный свидетель того, что жизнь всё равно сильнее разрушений.</t>
-  </si>
-  <si>
-    <t>На Тумском острове есть храм, который на первый взгляд напоминает хитроумную шкатулку с двойным дном. Снаружи — обычное готическое чудо с башенками и арками, а внутри вдруг оказывается два уровня: верхний для света, нижний для тени. И каждый этаж словно живёт своей жизнью — как будто вы попали в дом, где два поколения не разговаривают друг с другом, но всё равно мирно делят крышу.</t>
-  </si>
-  <si>
-    <t>Самое удивительное в этой церкви — её двойная натура. Нижний уровень, посвящённый Святому Варфоломею, выглядит сурово и основательно, словно крепость, готовая выдержать любой натиск. Здесь низкие своды и тёмные углы, где хочется шептаться, а не разговаривать вслух.</t>
-  </si>
-  <si>
-    <t>А верхний уровень, посвящённый Святому Кресту, напротив, весь соткан из воздуха и света. Огромные окна впускают солнце, своды стремятся к небу, и создаётся впечатление, что храм сам по себе поёт. Здесь когда-то сидели каноники, здесь же и сейчас музыка органа разливается так, будто стены умеют дышать.</t>
-  </si>
-  <si>
-    <t>Есть в этой церкви и маленькая загадка, достойная хорошей городской легенды. Князь Генрик IV хотел, чтобы его похоронили именно здесь, в нижнем храме, «пока не построят мавзолей». Но судьба оказалась насмешливой: мавзолей так и не появился, а во время Второй мировой его останки куда-то исчезли. Одни говорят — увезли немцы, другие шепчут — сам ушёл, чтобы больше не смотреть на войны.</t>
-  </si>
-  <si>
-    <t>И ещё: в отличие от многих храмов, где пространство строго вертикально — от земли к небу, здесь всё устроено горизонтально-вертикально одновременно. Два этажа, два характера, два пути. Словно храм не выбирает между светом и тьмой, а даёт каждому своё место. И, возможно, именно поэтому он кажется живым — потому что признаёт в человеке и земное, и небесное сразу.</t>
+    <t>В 1163 году князь Болеслав Высокий, впечатленный стратегическим расположением, построил здесь свою резиденцию: старый деревянный город сменился мощными кирпичными стенами и строениями в романском стиле. А в 1315 году остров был «переписан» церкви — и превратился в духовное убежище, где тот, кто нарушил закон, мог найти защиту под крышей каноников.</t>
+  </si>
+  <si>
+    <t>В 1315 году весь остров Тумский был продан церковным властям, и с этого времени на острове прекратила действовать светская юрисдикция, которой часто пользовались нарушители светских законов во Вроцлаве. Проявлением специфического законодательства, действовавшего на острове Тумский, была обязанность снимать головной убор при въезде на Тумский мост, где находился пограничный знак небольшого «церковного государства». Эта обязанность распространялась даже на коронованных особ.</t>
+  </si>
+  <si>
+    <t>Николай Коперник временно жил на острове Тумском , а в 1503–1538 годах был священнослужителем в Костёле Святого Креста. В 1766 году во время своего визита во Вроцлав Джакомо Казанова остановился у отца Бастиани на острове Тумском.</t>
+  </si>
+  <si>
+    <t>Остров Тумский, кажется, сначала был всего лишь цепочкой деревянных домов, уютно устроившихся между костёлом Святого Мартина и костёлом Святого Креста. В XI веке княжеская часовня Святого Мартина уже отважно стояла среди укреплённых стен, а река Одра лениво обвивала остров, снабжая жителей продовольствием и выступая естественной защитой. Тогда здесь проживало около полутора тысяч человек, и каждый из них, наверняка, знал, где прячется лучшая рыба и какой ветер предвещает бурю.</t>
+  </si>
+  <si>
+    <t>В 1315 году Тумский окончательно сменил хозяев и превратился в маленькое, но гордое «церковное государство», где мирские законы больше не действовали, а вместо них царили правила, придуманные, кажется, исключительно ради удовольствия самих правил. Например, каждый въезжающий на Тумский мост обязан был снять головной убор — и неважно, простой ли это сапожник или коронованная особа, — потому что таков был местный порядок. И нарушать его не приходило в голову даже самым отчаянным бунтарям: мало ли что у этих священнослужителей ещё записано в уставе, вдруг следующее правило — стоять на одной ноге и петь псалмы при входе на остров?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда-то Тумский был настоящим островом, с гордостью соединенным с миром мостами — одним в сторону Пясек, другим в сторону правого берега Одры. Но Вроцлаву однажды наскучили собственные укрепления: в 1807 году их дружно снесли, рвы засыпали, а островом Тумский остался только по названию. С тех пор у него лишь одна островная реликвия — пруд в Ботаническом саду, скромный осколок когда-то шумного речного русла. </t>
+  </si>
+  <si>
+    <t>Святая Ядвига</t>
+  </si>
+  <si>
+    <t>Одно из самых примечательных явлений на Тумском мосту — вовсе не толпы туристов с фотоаппаратами, а каменная дама, величественно возвышающаяся на неоготическом пьедестале у входа со стороны Песчаного острова. Это святая Ядвига, покровительница Силезии, которая, кажется, смотрит не столько на город, сколько сквозь него — туда, где продолжается её собственная вечная история.</t>
+  </si>
+  <si>
+    <t>Через дорогу ей компанию составляет святой Иоанн Креститель — тоже не последний человек в небесной иерархии и официальный защитник Вроцлава и его собора. Автор скульптуры, Густав Грюненберг, оставил его здесь в 1893 году, и с тех пор оба святителя бодро охраняют мост, словно сторожа между мирами.</t>
+  </si>
+  <si>
+    <t>Ядвига, как и положено, облачена в длинный плащ и митру, а в руке держит крошечный храм — модель Тшебницкого костёла. Смотрится так, будто она вот-вот предложит его прохожему: мол, держи, это тебе, только не потеряй.</t>
+  </si>
+  <si>
+    <t>Ядвига появилась на свет где-то около 1174 года, в Венгрии, но, похоже, сама судьба сразу приготовила ей билет в Силезию. В двенадцать лет её выдали замуж за Генрика Бородатого — звучит так, будто девочке просто подарили бородатого мужа в красивой коробке с ленточкой. Но, к счастью, подарок оказался не разочарованием: их союз был удивительно счастливым и плодотворным, а вместе они управляли землёй, строили монастыри, церкви и укрепляли христианство так, будто занимались не политикой, а чем-то вроде садоводства.</t>
+  </si>
+  <si>
+    <t>Герцогского замка, где Ядвига когда-то жила, уже давно нет — стерся с лица земли ещё в XIV веке. Но кое-что упрямо пережило время. В западной части бывшего острова можно набрести на монастырь сестёр школы Нотр-Дам на улице Святого Марцина, 12. Там и стены помнят больше, чем рассказывают: остатки готической комнаты с крошечным окошком, из которого, говорят, княгиня сама раздавала еду беднякам. Представляете: открывается окошко, и вместе с куском хлеба в мир просачивается чуть-чуть небесного света.</t>
+  </si>
+  <si>
+    <t>Когда Генрик умер в 1238 году, Ядвига не растерялась — решила целиком посвятить себя Богу. Основала цистерцианский монастырь в Тшебнице, поселилась там сама и, как говорят, чувствовала себя совершенно на своём месте. Через три десятка лет после её смерти Папа Климент IV официально подтвердил: да, это святая, сомнений нет. Так Ядвига стала первой канонизированной святой польского происхождения и получила вечный небесный титул, куда более почётный, чем княжеский.</t>
+  </si>
+  <si>
+    <t>С тех пор её помнят и почитают: каждый год 16 октября Силезия вспоминает свою святую покровительницу. В Тшебнице хранятся её мощи, туда тянутся паломники, а её образ до сих пор вдохновляет художников. Обычно на картинах она в монашеском облачении с короной — и это очень точно: одновременно скромная служительница и княжна, символ милосердия и силы. Впрочем, если присмотреться, в её каменном взгляде можно уловить и лёгкую загадочную улыбку — ту самую, что остаётся у тех, кто знает куда больше, чем готов рассказать.</t>
   </si>
 </sst>
 </file>
@@ -535,7 +577,7 @@
     <col min="3" max="3" width="41.1640625" customWidth="1"/>
     <col min="4" max="4" width="55.83203125" customWidth="1"/>
     <col min="5" max="5" width="50.6640625" customWidth="1"/>
-    <col min="6" max="6" width="85.6640625" customWidth="1"/>
+    <col min="6" max="6" width="61.6640625" customWidth="1"/>
     <col min="7" max="7" width="51.1640625" customWidth="1"/>
     <col min="8" max="8" width="48.1640625" customWidth="1"/>
   </cols>
@@ -566,12 +608,26 @@
         <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="145" customHeight="1" x14ac:dyDescent="0.2">
@@ -579,25 +635,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="I3" s="2"/>
     </row>
@@ -606,25 +662,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -633,78 +689,104 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="204" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
